--- a/extracted_urls/autonews/autonews_urls.xlsx
+++ b/extracted_urls/autonews/autonews_urls.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Body is just a date and a featured-story teaser, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a featured-story blurb about marketing leadership, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Body is just a date and a featured-story link, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is just a dated featured-stories link and not a substantive engineering article.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Body is just a featured-stories promo with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a featured-stories promo with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Body is just a newsletter/featured-stories index with no engineering article narrative.</t>
+          <t>Body is just a newsletter header and a featured-story link, with no substantive engineering article.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Body is just a headline/date repeat with no substantive engineering or R&amp;D content.</t>
+          <t>Body is essentially a headline/date stub with no engineering narrative or technical detail.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Body is mostly sales-market commentary and executive remarks, with no substantive engineering or R&amp;D detail.</t>
+          <t>Body is mostly market commentary and executive remarks, with no substantive engineering or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Body is just a brief sales/market note with executive comments, not engineering or R&amp;D substance.</t>
+          <t>Body is just sales commentary and an auto show quote with no engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Body is just a brief business mention and a panel teaser, with no engineering or technical substance about the EVs or plant.</t>
+          <t>Body is mostly a brief market/policy blurb with no engineering detail beyond a JV mention.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Body is mostly a short policy request with no engineering or R&amp;D substance.</t>
+          <t>Body is mostly a brief policy note and executive panel blurb, with no real engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-story link and date block, with no substantive engineering narrative.</t>
+          <t>The body is essentially a featured-story link with no substantive article narrative or engineering detail.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Body is just a headline/date and a featured-story link, with no substantive engineering content.</t>
+          <t>Body is just a headline and featured-story navigation with no substantive engineering content.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Body is mostly a pricing/photo caption plus a trade panel mention, with no substantive engineering or R&amp;D detail.</t>
+          <t>Body is mostly a pricing/market-position blurb with no substantive engineering or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Body is essentially just a headline and featured-story link, with no substantive engineering narrative.</t>
+          <t>Body is just a headline/date and featured-story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Body is just a headline/date and a featured-story link, with no substantive engineering article narrative.</t>
+          <t>Body is just a headline/date and featured-story link, with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Body is just an attendance record and a vague executive panel quote, with no real engineering or R&amp;D substance.</t>
+          <t>Body is just attendance/news event coverage with no engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Body is mostly a headline and featured-story link with no substantive engineering narrative.</t>
+          <t>Body is just a headline and featured-story link with no substantive testing narrative or engineering detail.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Body is a theft anecdote with no engineering, validation, or technical content.</t>
+          <t>Body is a retail misconduct story with no engineering, R&amp;D, or technical content.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Body is mostly headline and a brief production note, with no substantive engineering or R&amp;D detail.</t>
+          <t>Body is mostly a headline and unrelated event blurb, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Body is mostly a brief redesign blurb and trade-show quote, with no substantive engineering or validation detail.</t>
+          <t>Body is mostly a brief redesign blurb and event-style commentary, with no substantive engineering or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Body is a brief forum summary about fuel prices and trade policy, with no substantive engineering or R&amp;D detail.</t>
+          <t>Body is mostly a forum quote and executive commentary on fuel prices and trade, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Body is just a podcast/featured-stories stub with no substantive engineering narrative.</t>
+          <t>The body is just a podcast-style teaser and featured story link, with no substantive engineering or R&amp;D discussion.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Body is just a newsletter header and a featured-story link, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a newsletter header and featured-story link, with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Body is just a headline and featured-story link with no substantive engineering narrative.</t>
+          <t>Body is just a headline/date and featured-story link with no engineering narrative or technical detail.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>The body is just a sponsor/title stub with no substantive article narrative or engineering content.</t>
+          <t>Body is essentially a report landing page with no substantive engineering or R&amp;D narrative, and the topic is dealer fraud rather than automotive development.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Landing-page style body with only report title and sponsor, no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a report landing page with no technical article narrative or engineering detail.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Body is just a report landing page with no engineering narrative, only finance-market metadata and a title.</t>
+          <t>Body is just a report landing page with no substantive engineering narrative, focused on finance trends rather than R&amp;D.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Body is just a headline and sponsor text with no engineering or article narrative.</t>
+          <t>Body is just a title/landing-page snippet with no substantive engineering content.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Body is just a title/header stub with no substantive engineering article or technical detail.</t>
+          <t>Body is just a title/header with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Body is just a promo header with no substantive engineering narrative, analysis, or technical detail.</t>
+          <t>Body is just a promotional headline with no substantive engineering or automotive R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Body is just a webinar/promo teaser with no technical article content, so it’s not relevant to automotive R&amp;D or engineering.</t>
+          <t>Body is just a webinar/promo header with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>The body is just a headline and featured-story link, with no substantive engineering or R&amp;D article content.</t>
+          <t>Body is just a headline and a featured-story link, with no substantive engineering article narrative.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>This is just a webcast signup/form page with no engineering article body or automotive R&amp;D substance.</t>
+          <t>Body is just a webcast registration form with no engineering article content.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Body is just a webcast form and registration prompt, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a webcast registration form with no engineering article content.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Body is just a trade-policy blurb with no engineering or R&amp;D substance.</t>
+          <t>Body is just a brief trade-policy quote and event panel mention, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Body is just a brief trade/event summary with no engineering or R&amp;D substance.</t>
+          <t>Body is mostly a brief trade-policy blurb with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Body is mostly a vandalism/news snippet plus an unrelated auto-show quote, with no engineering or R&amp;D content.</t>
+          <t>Body is about dealership vandalism and a stray show-panel sentence, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Body is essentially a headline and featured-story link, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is essentially a headline and featured-story teaser, with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Body is mostly about EV lease supply and policy commentary, with no substantive engineering or R&amp;D detail.</t>
+          <t>Body is mostly a brief market/industry note about off-lease EVs and executive comments, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Body is just a congress speaker promo with a featured-story link, not an engineering article.</t>
+          <t>Body is just a speaker announcement and featured-story link, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>

--- a/extracted_urls/autonews/autonews_urls.xlsx
+++ b/extracted_urls/autonews/autonews_urls.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Body is just a featured-story blurb about marketing leadership, with no engineering or R&amp;D substance.</t>
+          <t>Body is just a featured-story teaser and metadata, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Body is just a dated featured-stories link and not a substantive engineering article.</t>
+          <t>Body is just a date and a featured-story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Body is just a featured-stories promo with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is just a featured-stories promo block with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Body is just a newsletter header and a featured-story link, with no substantive engineering article.</t>
+          <t>Body is just a newsletter-style featured story link with no substantive engineering article narrative.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Body is essentially a headline/date stub with no engineering narrative or technical detail.</t>
+          <t>Body is just a headline/date and link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Body is mostly market commentary and executive remarks, with no substantive engineering or R&amp;D detail.</t>
+          <t>Mostly sales-market commentary with a brief EV adoption note; no substantive engineering or R&amp;D detail in the body.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Body is just sales commentary and an auto show quote with no engineering or R&amp;D content.</t>
+          <t>Body is a brief sales and trade-comment snippet with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Body is mostly a brief market/policy blurb with no engineering detail beyond a JV mention.</t>
+          <t>Body is mostly a brief note and event-panel quote with no engineering detail or substantive R&amp;D content.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Body is mostly a brief policy note and executive panel blurb, with no real engineering or R&amp;D substance.</t>
+          <t>Body is mostly a policy headline and a brief exec-panel summary, with no substantive engineering or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-04-01T16:36:23.798Z</t>
+          <t>2026-04-02T06:34:00.611Z</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>The body is essentially a featured-story link with no substantive article narrative or engineering detail.</t>
+          <t>Body is essentially a featured-story link with no substantive article narrative or engineering detail.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Body is just a headline and featured-story navigation with no substantive engineering content.</t>
+          <t>Body contains only a headline and featured-story link, with no engineering or technical article content.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-04-01T15:39:28.948Z</t>
+          <t>2026-04-02T06:34:57.31Z</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Body is mostly a pricing/market-position blurb with no substantive engineering or R&amp;D detail.</t>
+          <t>Body is mostly a price comparison and a brief event-style blurb, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Body is just a headline/date and featured-story link, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is essentially just a headline/date and featured-story link, with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Body is just a headline/date and featured-story link, with no substantive engineering narrative.</t>
+          <t>Body is just a headline/date plus a featured-story link, with no substantive engineering or article narrative.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Body is just attendance/news event coverage with no engineering or R&amp;D content.</t>
+          <t>Body is mostly event attendance and a brief executive panel mention, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-04-01T11:10:04.04Z</t>
+          <t>2026-04-02T06:21:59.163Z</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Body is just a headline and featured-story link with no substantive testing narrative or engineering detail.</t>
+          <t>The body is mostly a headline and featured-story navigation with no substantive article narrative or engineering detail.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Body is a retail misconduct story with no engineering, R&amp;D, or technical content.</t>
+          <t>Body is a service-theft incident with no engineering or R&amp;D substance, plus unrelated trade-show boilerplate.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Body is mostly a headline and unrelated event blurb, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly a headline and trade-show blurb with no substantive engineering or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Body is mostly a brief redesign blurb and event-style commentary, with no substantive engineering or R&amp;D detail.</t>
+          <t>Body is mostly a brief redesign note and show commentary, with no substantive engineering or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Body is mostly a forum quote and executive commentary on fuel prices and trade, with no engineering or R&amp;D substance.</t>
+          <t>Body is just a brief forum panel summary about fuel prices and trade, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>The body is just a podcast-style teaser and featured story link, with no substantive engineering or R&amp;D discussion.</t>
+          <t>Body is just a featured-stories/podcast teaser with no substantive engineering narrative or technical detail.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Body is just a newsletter header and featured-story link, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is just a newsletter-style teaser and featured story link, with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Body is just a headline/date and featured-story link with no engineering narrative or technical detail.</t>
+          <t>Body is essentially a headline and featured-story link, with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Body is essentially a report landing page with no substantive engineering or R&amp;D narrative, and the topic is dealer fraud rather than automotive development.</t>
+          <t>Body is essentially a title/partner landing page with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Body is just a report landing page with no technical article narrative or engineering detail.</t>
+          <t>Landing-page style body with only report title and publisher, no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Body is just a report landing page with no substantive engineering narrative, focused on finance trends rather than R&amp;D.</t>
+          <t>Body is just a report landing page with no substantive engineering or R&amp;D narrative, only finance-report labeling.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Body is just a title/landing-page snippet with no substantive engineering content.</t>
+          <t>Body is just a promo header with no substantive technical article or engineering detail.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Body is just a title/header with no substantive engineering article content.</t>
+          <t>Body is just a teaser/landing snippet with no substantive technical article content or engineering detail.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Body is just a promotional headline with no substantive engineering or automotive R&amp;D narrative.</t>
+          <t>Body is just a promo headline with no substantive engineering article narrative or technical details.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Body is just a webinar/promo header with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a webinar/promo headline with no engineering or automotive R&amp;D substance.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Body is just a headline and a featured-story link, with no substantive engineering article narrative.</t>
+          <t>Body is just a headline and featured-story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Body is just a webcast registration form with no engineering article content.</t>
+          <t>This is a webinar registration page with form fields, not a substantive engineering article.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Body is just a brief trade-policy quote and event panel mention, with no engineering or R&amp;D substance.</t>
+          <t>Body is just a trade-policy blurb with no engineering or technical article content.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Body is mostly a brief trade-policy blurb with no engineering or R&amp;D substance.</t>
+          <t>Body is mostly a brief trade-policy note with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Body is about dealership vandalism and a stray show-panel sentence, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly a crime blurb with no engineering or R&amp;D content; remaining sentence is unrelated auto-show commentary.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Body is essentially a headline and featured-story teaser, with no substantive engineering narrative.</t>
+          <t>Body is essentially a headline and featured-story link, with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Body is mostly a brief market/industry note about off-lease EVs and executive comments, with no engineering or R&amp;D substance.</t>
+          <t>Body is mostly a brief market-note about off-lease EVs and policy comments, with no substantive engineering or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Body is just a speaker announcement and featured-story link, with no engineering or R&amp;D substance.</t>
+          <t>Body is just a congress speaker notice and featured-story link, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
